--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T15:08:49+00:00</t>
+    <t>2026-07-01T07:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T07:03:00+00:00</t>
+    <t>2026-07-01T08:10:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:10:51+00:00</t>
+    <t>2026-07-01T14:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:14:35+00:00</t>
+    <t>2026-07-02T07:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T07:31:32+00:00</t>
+    <t>2026-07-02T18:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T18:50:30+00:00</t>
+    <t>2026-07-03T07:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:01:21+00:00</t>
+    <t>2026-07-03T07:53:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:53:06+00:00</t>
+    <t>2026-07-04T06:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T06:47:13+00:00</t>
+    <t>2026-07-06T08:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:19:21+00:00</t>
+    <t>2026-07-06T11:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:30:59+00:00</t>
+    <t>2026-07-07T07:34:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T07:34:33+00:00</t>
+    <t>2026-07-07T09:30:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T09:30:03+00:00</t>
+    <t>2026-07-07T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T16:17:51+00:00</t>
+    <t>2026-07-07T18:51:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T18:51:54+00:00</t>
+    <t>2026-07-08T06:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T06:29:02+00:00</t>
+    <t>2026-07-08T13:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T13:11:45+00:00</t>
+    <t>2026-07-09T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T07:37:59+00:00</t>
+    <t>2026-07-10T07:33:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T07:33:56+00:00</t>
+    <t>2026-07-11T06:13:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T06:13:55+00:00</t>
+    <t>2026-07-12T06:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-12T06:33:38+00:00</t>
+    <t>2026-07-13T06:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T06:51:55+00:00</t>
+    <t>2026-07-14T06:10:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T06:10:10+00:00</t>
+    <t>2026-07-15T06:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:13:44+00:00</t>
+    <t>2026-07-16T06:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T06:16:18+00:00</t>
+    <t>2026-07-17T06:14:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:14:46+00:00</t>
+    <t>2026-07-18T06:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-18T06:04:03+00:00</t>
+    <t>2026-07-19T06:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T06:29:36+00:00</t>
+    <t>2026-07-20T06:45:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T06:45:38+00:00</t>
+    <t>2026-07-21T06:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T06:27:40+00:00</t>
+    <t>2026-07-22T06:27:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T06:27:15+00:00</t>
+    <t>2026-07-23T06:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T06:30:53+00:00</t>
+    <t>2026-07-24T06:26:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T06:26:28+00:00</t>
+    <t>2026-07-25T06:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T06:16:33+00:00</t>
+    <t>2026-07-26T06:35:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/main/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T06:35:59+00:00</t>
+    <t>2026-07-27T07:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
